--- a/exports/trend_1d/CAMS_full_report.xlsx
+++ b/exports/trend_1d/CAMS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.48</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H2" t="n">
-        <v>364.4</v>
+        <v>343.5</v>
       </c>
       <c r="I2" t="n">
         <v>348.0581012223565</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K2" t="n">
-        <v>35.92</v>
+        <v>28.12</v>
       </c>
       <c r="L2" t="n">
         <v>6.01</v>
@@ -555,7 +578,7 @@
         <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>3.24</v>
+        <v>5.74</v>
       </c>
       <c r="O2" t="n">
         <v>-0.07000000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>15.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44301</v>
+        <v>44302</v>
       </c>
       <c r="H3" t="n">
-        <v>370.9</v>
+        <v>413.4</v>
       </c>
       <c r="I3" t="n">
         <v>388.8323521341338</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.98</v>
+        <v>-20.35</v>
       </c>
       <c r="L3" t="n">
-        <v>12.9</v>
+        <v>22.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.19</v>
       </c>
       <c r="N3" t="n">
-        <v>3.43</v>
+        <v>11.46</v>
       </c>
       <c r="O3" t="n">
         <v>-5.74</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.25</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44461</v>
+        <v>44462</v>
       </c>
       <c r="H4" t="n">
-        <v>686.6</v>
+        <v>681.1</v>
       </c>
       <c r="I4" t="n">
         <v>683.6705272675079</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K4" t="n">
-        <v>66.09</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>10.23</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.79</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H5" t="n">
-        <v>547.8</v>
+        <v>566.3</v>
       </c>
       <c r="I5" t="n">
         <v>565.0586915238416</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5" t="n">
-        <v>19.57</v>
+        <v>16.86</v>
       </c>
       <c r="L5" t="n">
         <v>2.89</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.4</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H6" t="n">
-        <v>568.2</v>
+        <v>542.6</v>
       </c>
       <c r="I6" t="n">
         <v>552.0210295817618</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>0.34</v>
+        <v>-4.19</v>
       </c>
       <c r="L6" t="n">
-        <v>3.27</v>
+        <v>4.54</v>
       </c>
       <c r="M6" t="n">
         <v>0.62</v>
       </c>
       <c r="N6" t="n">
-        <v>2.34</v>
+        <v>4.51</v>
       </c>
       <c r="O6" t="n">
         <v>3.38</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>10.09</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H7" t="n">
-        <v>553</v>
+        <v>580.4</v>
       </c>
       <c r="I7" t="n">
         <v>566.034559468039</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.92</v>
+        <v>-6.97</v>
       </c>
       <c r="L7" t="n">
-        <v>4.64</v>
+        <v>8.66</v>
       </c>
       <c r="M7" t="n">
         <v>1.67</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>4.95</v>
       </c>
       <c r="O7" t="n">
         <v>-4.51</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44601</v>
+        <v>44602</v>
       </c>
       <c r="H8" t="n">
-        <v>531.8</v>
+        <v>519.7</v>
       </c>
       <c r="I8" t="n">
         <v>530.3211997317459</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.369999999999999</v>
+        <v>-10.46</v>
       </c>
       <c r="L8" t="n">
-        <v>9.15</v>
+        <v>11.1</v>
       </c>
       <c r="M8" t="n">
         <v>0.62</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H9" t="n">
-        <v>494.6</v>
+        <v>514.9</v>
       </c>
       <c r="I9" t="n">
         <v>506.5157801653644</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" t="n">
-        <v>4.83</v>
+        <v>0.92</v>
       </c>
       <c r="L9" t="n">
         <v>4.21</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H10" t="n">
-        <v>479.6</v>
+        <v>472.2</v>
       </c>
       <c r="I10" t="n">
         <v>475.1632865168521</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.86</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>8.84</v>
+        <v>9.85</v>
       </c>
       <c r="M10" t="n">
         <v>2.93</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.66</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H11" t="n">
-        <v>465.1</v>
+        <v>481.8</v>
       </c>
       <c r="I11" t="n">
         <v>467.065925543871</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5</v>
+        <v>-2.03</v>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
         <v>2.45</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>12.95</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44739</v>
+        <v>44740</v>
       </c>
       <c r="H12" t="n">
-        <v>459.6</v>
+        <v>451.6</v>
       </c>
       <c r="I12" t="n">
         <v>457.3577509419213</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.61</v>
+        <v>-6.27</v>
       </c>
       <c r="L12" t="n">
-        <v>5.35</v>
+        <v>6.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.47</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>13.3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44770</v>
+        <v>44771</v>
       </c>
       <c r="H13" t="n">
-        <v>486.7</v>
+        <v>491.5</v>
       </c>
       <c r="I13" t="n">
         <v>487.9868360380183</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.77</v>
+        <v>-8.84</v>
       </c>
       <c r="L13" t="n">
-        <v>8.720000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>1.18</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.62</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44791</v>
+        <v>44792</v>
       </c>
       <c r="H14" t="n">
-        <v>475.7</v>
+        <v>451.1</v>
       </c>
       <c r="I14" t="n">
         <v>460.6034900508902</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.21</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>6.57</v>
+        <v>8.81</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>0.36</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>5.17</v>
       </c>
       <c r="O14" t="n">
         <v>0.99</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>12.02</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44812</v>
+        <v>44813</v>
       </c>
       <c r="H15" t="n">
-        <v>474.3</v>
+        <v>492.2</v>
       </c>
       <c r="I15" t="n">
         <v>482.5186510064055</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.14</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>5.54</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>3.77</v>
       </c>
       <c r="O15" t="n">
         <v>-5.17</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44868</v>
+        <v>44869</v>
       </c>
       <c r="H16" t="n">
-        <v>494.6</v>
+        <v>490.7</v>
       </c>
       <c r="I16" t="n">
         <v>490.7099617219434</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" t="n">
-        <v>0.49</v>
+        <v>-0.3</v>
       </c>
       <c r="L16" t="n">
         <v>3.29</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44945</v>
+        <v>44946</v>
       </c>
       <c r="H17" t="n">
-        <v>461.3</v>
+        <v>463.8</v>
       </c>
       <c r="I17" t="n">
         <v>462.2473515780405</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K17" t="n">
-        <v>5.99</v>
+        <v>5.48</v>
       </c>
       <c r="L17" t="n">
         <v>2.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.18</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H18" t="n">
-        <v>449.7</v>
+        <v>445.5</v>
       </c>
       <c r="I18" t="n">
         <v>447.632008397858</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.04</v>
+        <v>-3.95</v>
       </c>
       <c r="L18" t="n">
         <v>4.92</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.4</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H19" t="n">
-        <v>432</v>
+        <v>435.2</v>
       </c>
       <c r="I19" t="n">
         <v>432.6813635512966</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>3.03</v>
+        <v>2.31</v>
       </c>
       <c r="L19" t="n">
         <v>0.9399999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H20" t="n">
-        <v>412.9</v>
+        <v>406.9</v>
       </c>
       <c r="I20" t="n">
         <v>409.1266536365948</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.12</v>
+        <v>-6.5</v>
       </c>
       <c r="L20" t="n">
-        <v>5.33</v>
+        <v>6.89</v>
       </c>
       <c r="M20" t="n">
         <v>0.02</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45068</v>
+        <v>45069</v>
       </c>
       <c r="H21" t="n">
-        <v>427</v>
+        <v>438.2</v>
       </c>
       <c r="I21" t="n">
         <v>435.8994259694528</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.94</v>
+        <v>-7.69</v>
       </c>
       <c r="L21" t="n">
-        <v>6.17</v>
+        <v>7.89</v>
       </c>
       <c r="M21" t="n">
         <v>0.72</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.13</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H22" t="n">
-        <v>475.1</v>
+        <v>471.2</v>
       </c>
       <c r="I22" t="n">
         <v>472.766957703205</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K22" t="n">
-        <v>8.42</v>
+        <v>7.53</v>
       </c>
       <c r="L22" t="n">
         <v>2.97</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H23" t="n">
-        <v>492.9</v>
+        <v>520.9</v>
       </c>
       <c r="I23" t="n">
         <v>506.3805157700788</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.61</v>
+        <v>-10.55</v>
       </c>
       <c r="L23" t="n">
-        <v>6.28</v>
+        <v>11.52</v>
       </c>
       <c r="M23" t="n">
-        <v>0.47</v>
+        <v>1.48</v>
       </c>
       <c r="N23" t="n">
-        <v>2.66</v>
+        <v>5.68</v>
       </c>
       <c r="O23" t="n">
         <v>-0.82</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.59</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H24" t="n">
-        <v>480.6</v>
+        <v>460.3</v>
       </c>
       <c r="I24" t="n">
         <v>478.968397194384</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.74</v>
+        <v>-11.63</v>
       </c>
       <c r="L24" t="n">
-        <v>9.140000000000001</v>
+        <v>11.84</v>
       </c>
       <c r="M24" t="n">
         <v>1.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.44</v>
+        <v>4.22</v>
       </c>
       <c r="O24" t="n">
         <v>5.68</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>12.07</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="H25" t="n">
-        <v>485.1</v>
+        <v>497.2</v>
       </c>
       <c r="I25" t="n">
         <v>494.4478654257713</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.39</v>
+        <v>-8.02</v>
       </c>
       <c r="L25" t="n">
-        <v>7.1</v>
+        <v>8.41</v>
       </c>
       <c r="M25" t="n">
-        <v>1.54</v>
+        <v>2.87</v>
       </c>
       <c r="N25" t="n">
         <v>5.61</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.98</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H26" t="n">
-        <v>582.8</v>
+        <v>549</v>
       </c>
       <c r="I26" t="n">
         <v>571.6031618504261</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K26" t="n">
-        <v>17.22</v>
+        <v>10.42</v>
       </c>
       <c r="L26" t="n">
         <v>0.93</v>
@@ -1923,7 +2234,7 @@
         <v>1.42</v>
       </c>
       <c r="N26" t="n">
-        <v>4.12</v>
+        <v>5.8</v>
       </c>
       <c r="O26" t="n">
         <v>2.49</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>17.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="H27" t="n">
-        <v>630.3</v>
+        <v>647.7</v>
       </c>
       <c r="I27" t="n">
         <v>640.5361780826822</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.81</v>
+        <v>-17.98</v>
       </c>
       <c r="L27" t="n">
         <v>20.22</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.47</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H28" t="n">
-        <v>873.7</v>
+        <v>798.2</v>
       </c>
       <c r="I28" t="n">
         <v>806.6898578630742</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K28" t="n">
-        <v>34.89</v>
+        <v>23.24</v>
       </c>
       <c r="L28" t="n">
         <v>6.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="N28" t="n">
-        <v>6.96</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O28" t="n">
         <v>2.76</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>20.07</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45580</v>
+        <v>45581</v>
       </c>
       <c r="H29" t="n">
-        <v>925.3</v>
+        <v>967.3</v>
       </c>
       <c r="I29" t="n">
         <v>929.429284256037</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K29" t="n">
-        <v>-15.92</v>
+        <v>-21.19</v>
       </c>
       <c r="L29" t="n">
-        <v>19.62</v>
+        <v>23.03</v>
       </c>
       <c r="M29" t="n">
         <v>4.07</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>13.28</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H30" t="n">
-        <v>900.1</v>
+        <v>863.1</v>
       </c>
       <c r="I30" t="n">
         <v>866.8530399979904</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.95</v>
+        <v>-10.77</v>
       </c>
       <c r="L30" t="n">
-        <v>10.37</v>
+        <v>11.28</v>
       </c>
       <c r="M30" t="n">
         <v>0.44</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>16.92</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="H31" t="n">
-        <v>970</v>
+        <v>978.7</v>
       </c>
       <c r="I31" t="n">
         <v>976.0179640265467</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.39</v>
+        <v>-13.39</v>
       </c>
       <c r="L31" t="n">
-        <v>15.84</v>
+        <v>16.16</v>
       </c>
       <c r="M31" t="n">
         <v>1.36</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>10.09</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H32" t="n">
-        <v>975.8</v>
+        <v>941.6</v>
       </c>
       <c r="I32" t="n">
         <v>956.648110295716</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.3</v>
+        <v>-3.79</v>
       </c>
       <c r="L32" t="n">
-        <v>1.13</v>
+        <v>3.95</v>
       </c>
       <c r="M32" t="n">
         <v>3.09</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.61</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H33" t="n">
-        <v>685</v>
+        <v>720.4</v>
       </c>
       <c r="I33" t="n">
         <v>716.8350455273489</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K33" t="n">
-        <v>27.25</v>
+        <v>23.49</v>
       </c>
       <c r="L33" t="n">
         <v>4.69</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.66</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H34" t="n">
-        <v>761.6</v>
+        <v>721.6</v>
       </c>
       <c r="I34" t="n">
         <v>733.8037629408748</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K34" t="n">
-        <v>5.72</v>
+        <v>0.17</v>
       </c>
       <c r="L34" t="n">
         <v>7</v>
@@ -2379,7 +2786,7 @@
         <v>9.050000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>4.19</v>
+        <v>5.25</v>
       </c>
       <c r="O34" t="n">
         <v>5.17</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.76</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45793</v>
+        <v>45796</v>
       </c>
       <c r="H35" t="n">
-        <v>778.2</v>
+        <v>790.3</v>
       </c>
       <c r="I35" t="n">
         <v>784.0166368755406</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.84</v>
+        <v>-9.52</v>
       </c>
       <c r="L35" t="n">
-        <v>8.9</v>
+        <v>10.53</v>
       </c>
       <c r="M35" t="n">
         <v>4.63</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.81</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H36" t="n">
-        <v>806.9</v>
+        <v>779.2</v>
       </c>
       <c r="I36" t="n">
         <v>794.6765031801054</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K36" t="n">
-        <v>2.1</v>
+        <v>-1.4</v>
       </c>
       <c r="L36" t="n">
         <v>2.86</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H37" t="n">
-        <v>778.1</v>
+        <v>802.7</v>
       </c>
       <c r="I37" t="n">
         <v>790.7469356210481</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K37" t="n">
-        <v>0.14</v>
+        <v>-3.02</v>
       </c>
       <c r="L37" t="n">
-        <v>3.32</v>
+        <v>3.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.29</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.36</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H38" t="n">
-        <v>776.6</v>
+        <v>773.7</v>
       </c>
       <c r="I38" t="n">
         <v>775.0392212960829</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.25</v>
+        <v>-3.61</v>
       </c>
       <c r="L38" t="n">
-        <v>3.43</v>
+        <v>3.9</v>
       </c>
       <c r="M38" t="n">
         <v>0.15</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="H39" t="n">
-        <v>785.8</v>
+        <v>802.9</v>
       </c>
       <c r="I39" t="n">
         <v>800.3571291256695</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.56</v>
+        <v>-3.77</v>
       </c>
       <c r="L39" t="n">
-        <v>3.92</v>
+        <v>5.08</v>
       </c>
       <c r="M39" t="n">
         <v>0.92</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.2</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H40" t="n">
-        <v>749.5</v>
+        <v>737.2</v>
       </c>
       <c r="I40" t="n">
         <v>745.1146049268195</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.65</v>
+        <v>-8.18</v>
       </c>
       <c r="L40" t="n">
         <v>8.710000000000001</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H41" t="n">
-        <v>672.7</v>
+        <v>704.85</v>
       </c>
       <c r="I41" t="n">
         <v>689.5886700980425</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K41" t="n">
-        <v>8.75</v>
+        <v>4.39</v>
       </c>
       <c r="L41" t="n">
         <v>5.11</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.5</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="H42" t="n">
-        <v>769.1</v>
+        <v>757.2</v>
       </c>
       <c r="I42" t="n">
         <v>757.5481534839396</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K42" t="n">
-        <v>9.119999999999999</v>
+        <v>7.43</v>
       </c>
       <c r="L42" t="n">
         <v>2.11</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.08</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H43" t="n">
-        <v>792.2</v>
+        <v>807.25</v>
       </c>
       <c r="I43" t="n">
         <v>795.7329870539734</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.62</v>
+        <v>-6.61</v>
       </c>
       <c r="L43" t="n">
-        <v>6.64</v>
+        <v>7.44</v>
       </c>
       <c r="M43" t="n">
         <v>1.57</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H44" t="n">
-        <v>776.6</v>
+        <v>749.8</v>
       </c>
       <c r="I44" t="n">
         <v>757.3873694543444</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.8</v>
+        <v>-7.12</v>
       </c>
       <c r="L44" t="n">
-        <v>4.46</v>
+        <v>7.84</v>
       </c>
       <c r="M44" t="n">
         <v>1.67</v>
       </c>
       <c r="N44" t="n">
-        <v>1.78</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
         <v>1.9</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H45" t="n">
-        <v>791</v>
+        <v>809.4</v>
       </c>
       <c r="I45" t="n">
         <v>808.06045958488</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.49</v>
+        <v>-7.95</v>
       </c>
       <c r="L45" t="n">
-        <v>8.699999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="M45" t="n">
         <v>1.74</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="H46" t="n">
-        <v>749.95</v>
+        <v>746</v>
       </c>
       <c r="I46" t="n">
         <v>749.0246694132541</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.34</v>
+        <v>-7.83</v>
       </c>
       <c r="L46" t="n">
         <v>8.289999999999999</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3123,6 +3686,14 @@
       <c r="Q47" t="n">
         <v>43</v>
       </c>
+      <c r="R47" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5735,7 +6306,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.1</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="6">
@@ -5745,7 +6316,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -5755,7 +6326,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
@@ -5765,7 +6336,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5775,7 +6346,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -5785,7 +6356,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102.6</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="11">
@@ -5795,7 +6366,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -5805,7 +6376,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -5815,7 +6386,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="14">
@@ -5825,7 +6396,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.86</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="15">
@@ -5835,7 +6406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.92</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
@@ -5845,7 +6416,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.33</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="17">
@@ -5855,7 +6426,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.09</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -5865,7 +6436,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="19">
@@ -5875,7 +6446,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.47</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="20">
@@ -5885,7 +6456,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -5895,7 +6466,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.22</v>
+        <v>23.03</v>
       </c>
     </row>
     <row r="22">
@@ -5905,7 +6476,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -5915,7 +6486,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5925,7 +6496,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="25">
@@ -5945,7 +6516,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="27">
@@ -5955,7 +6526,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.33</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="28">
@@ -5965,7 +6536,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
